--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.07626680020275</v>
+        <v>10.41239335503295</v>
       </c>
       <c r="D2" t="n">
-        <v>64.06298021118519</v>
+        <v>10.41023428431759</v>
       </c>
       <c r="E2" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F2" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>74.72439360804863</v>
+        <v>12.1427139613079</v>
       </c>
       <c r="D3" t="n">
-        <v>74.60584640586191</v>
+        <v>12.12345004095256</v>
       </c>
       <c r="E3" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F3" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.92466361587482</v>
+        <v>10.22525783757966</v>
       </c>
       <c r="D4" t="n">
-        <v>62.91940930545934</v>
+        <v>10.22440401213714</v>
       </c>
       <c r="E4" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F4" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.27295542804278</v>
+        <v>10.11935525705695</v>
       </c>
       <c r="D5" t="n">
-        <v>62.02749243308192</v>
+        <v>10.07946752037581</v>
       </c>
       <c r="E5" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F5" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.60764388343252</v>
+        <v>6.598742131057786</v>
       </c>
       <c r="D6" t="n">
-        <v>40.58574493702288</v>
+        <v>6.595183552266218</v>
       </c>
       <c r="E6" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.80072983292964</v>
+        <v>2.242618597851067</v>
       </c>
       <c r="D7" t="n">
-        <v>13.91272443637909</v>
+        <v>2.260817720911602</v>
       </c>
       <c r="E7" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F7" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.59921448092823</v>
+        <v>1.884872353150837</v>
       </c>
       <c r="D8" t="n">
-        <v>11.46235941771315</v>
+        <v>1.862633405378387</v>
       </c>
       <c r="E8" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F8" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.73297719961947</v>
+        <v>1.744108794938163</v>
       </c>
       <c r="D9" t="n">
-        <v>10.75336856678699</v>
+        <v>1.747422392102886</v>
       </c>
       <c r="E9" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F9" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.033179284177</v>
+        <v>5.042891633678762</v>
       </c>
       <c r="D10" t="n">
-        <v>30.93761714962153</v>
+        <v>5.0273627868135</v>
       </c>
       <c r="E10" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F10" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.87412721512592</v>
+        <v>6.317045672457962</v>
       </c>
       <c r="D11" t="n">
-        <v>37.75706808390913</v>
+        <v>6.135523563635233</v>
       </c>
       <c r="E11" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F11" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.91403519495502</v>
+        <v>6.648530719180191</v>
       </c>
       <c r="D12" t="n">
-        <v>9.7082439194738</v>
+        <v>1.577589636914493</v>
       </c>
       <c r="E12" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F12" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.71215332316215</v>
+        <v>8.07822491501385</v>
       </c>
       <c r="D13" t="n">
-        <v>49.12351288413089</v>
+        <v>7.98257084367127</v>
       </c>
       <c r="E13" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F13" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.47417968531061</v>
+        <v>10.31455419886298</v>
       </c>
       <c r="D14" t="n">
-        <v>62.72041624351777</v>
+        <v>10.19206763957164</v>
       </c>
       <c r="E14" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F14" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.45744246614466</v>
+        <v>8.686834400748507</v>
       </c>
       <c r="D15" t="n">
-        <v>33.15989532623116</v>
+        <v>5.388482990512563</v>
       </c>
       <c r="E15" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F15" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>67.61342229887131</v>
+        <v>10.98718112356659</v>
       </c>
       <c r="D16" t="n">
-        <v>56.00231508766515</v>
+        <v>9.100376201745586</v>
       </c>
       <c r="E16" t="n">
-        <v>20.55481779647705</v>
+        <v>3.340157891927521</v>
       </c>
       <c r="F16" t="n">
-        <v>21.63152411475221</v>
+        <v>3.515122668647234</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
